--- a/excel/Batch_04_Leads_Tracker.xlsx
+++ b/excel/Batch_04_Leads_Tracker.xlsx
@@ -398,23 +398,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:R21"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="52.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="36.83203125" customWidth="1"/>
+    <col min="7" max="7" width="52.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.83203125" customWidth="1"/>
+    <col min="11" max="11" width="52.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
+    <col min="14" max="14" width="36.83203125" customWidth="1"/>
+    <col min="15" max="15" width="52.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="19" max="19" width="32.83203125" customWidth="1"/>
+    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,33 +439,42 @@
         <v>Social Links</v>
       </c>
       <c r="F1" t="str">
+        <v>1st Email Subject</v>
+      </c>
+      <c r="G1" t="str">
         <v>1st Email</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Dates</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>Follow Up 1 Subject</v>
+      </c>
+      <c r="K1" t="str">
         <v>Follow Up 1</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Status</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Dates</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>Follow Up 2 Subject</v>
+      </c>
+      <c r="O1" t="str">
         <v>Follow Up 2</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Status</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Dates</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Lead Status</v>
       </c>
     </row>
@@ -480,9 +494,11 @@
       <c r="E2" t="str">
         <v/>
       </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Homepage redesign idea for Spring Clean London
-Hi Spring Clean London team,
+      <c r="F2" t="str">
+        <v>Homepage redesign idea for Spring Clean London</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Spring Clean London team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the current site uses a dated, copy-heavy structure and does not give mobile visitors a quick way to compare domestic, commercial, end-of-tenancy and carpet-cleaning options. This matters because busy customers may struggle to identify the right service or reach the quote step before leaving.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a clearer service hierarchy, stronger trust section, London coverage summary, recent-work gallery and a short quote form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -493,15 +509,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Sent</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Homepage redesign idea for Spring Clean London
-Hi Spring Clean London team,
+      <c r="J2" t="str">
+        <v>Following up — Homepage redesign idea for Spring Clean London</v>
+      </c>
+      <c r="K2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Spring Clean London team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a clearer service hierarchy, stronger trust section, London coverage summary, recent-work gallery and a short quote form. That would directly address the current issue where the current site uses a dated, copy-heavy structure and does not give mobile visitors a quick way to compare domestic, commercial, end-of-tenancy and carpet-cleaning options, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -511,15 +529,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J2" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Homepage redesign idea for Spring Clean London
-Hi Spring Clean London team,
+      <c r="L2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v>Final follow-up — Homepage redesign idea for Spring Clean London</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Spring Clean London team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a clearer service hierarchy, stronger trust section, London coverage summary, recent-work gallery and a short quote form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -528,13 +548,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M2" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -555,9 +575,11 @@
         <v xml:space="preserve">Facebook: https://www.instagram.com/pshahoptician/
 Facebook: https://www.facebook.com/pshahoptician/</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer online experience for P Shah Opticians
-Hi P Shah Opticians team,
+      <c r="F3" t="str">
+        <v>A clearer online experience for P Shah Opticians</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi P Shah Opticians team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage still gives prominent space to reopening and safety-era messaging, while appointments, eye-care services and frame selection are not presented through a strong modern booking journey. This matters because new patients can receive an outdated first impression and may not immediately see how to book an eye test.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a current appointment-led hero, clearer eye-care and frame sections, stronger patient proof, location information and a focused booking form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -568,15 +590,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Sent</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A clearer online experience for P Shah Opticians
-Hi P Shah Opticians team,
+      <c r="J3" t="str">
+        <v>Following up — A clearer online experience for P Shah Opticians</v>
+      </c>
+      <c r="K3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi P Shah Opticians team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a current appointment-led hero, clearer eye-care and frame sections, stronger patient proof, location information and a focused booking form. That would directly address the current issue where the homepage still gives prominent space to reopening and safety-era messaging, while appointments, eye-care services and frame selection are not presented through a strong modern booking journey, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -586,15 +610,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A clearer online experience for P Shah Opticians
-Hi P Shah Opticians team,
+      <c r="L3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v>Final follow-up — A clearer online experience for P Shah Opticians</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi P Shah Opticians team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a current appointment-led hero, clearer eye-care and frame sections, stronger patient proof, location information and a focused booking form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -603,13 +629,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M3" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -629,9 +655,11 @@
       <c r="E4" t="str">
         <v>Facebook: https://www.facebook.com/bespoketailorstudio/</v>
       </c>
-      <c r="F4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A more refined homepage for Bespoke Tailor Studio
-Hi Bespoke Tailor Studio team,
+      <c r="F4" t="str">
+        <v>A more refined homepage for Bespoke Tailor Studio</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Bespoke Tailor Studio team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the live homepage repeats the business name, headline and telephone content several times, weakening hierarchy and making the premium tailoring experience feel less polished. This matters because high-value clients may find it harder to understand the services, craftsmanship and consultation process quickly.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a refined editorial hero, clear bespoke and wedding service paths, craftsmanship gallery, fitting process, client proof and consultation form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -642,15 +670,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Sent</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A more refined homepage for Bespoke Tailor Studio
-Hi Bespoke Tailor Studio team,
+      <c r="J4" t="str">
+        <v>Following up — A more refined homepage for Bespoke Tailor Studio</v>
+      </c>
+      <c r="K4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Bespoke Tailor Studio team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a refined editorial hero, clear bespoke and wedding service paths, craftsmanship gallery, fitting process, client proof and consultation form. That would directly address the current issue where the live homepage repeats the business name, headline and telephone content several times, weakening hierarchy and making the premium tailoring experience feel less polished, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -660,15 +690,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A more refined homepage for Bespoke Tailor Studio
-Hi Bespoke Tailor Studio team,
+      <c r="L4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>Final follow-up — A more refined homepage for Bespoke Tailor Studio</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Bespoke Tailor Studio team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a refined editorial hero, clear bespoke and wedding service paths, craftsmanship gallery, fitting process, client proof and consultation form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -677,13 +709,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M4" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
@@ -704,9 +736,11 @@
         <v xml:space="preserve">Facebook: https://www.instagram.com/kingupholstery/
 Facebook: https://www.facebook.com/kingupholsteryn1/</v>
       </c>
-      <c r="F5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Showcasing King Upholstery’s craftsmanship online
-Hi King Upholstery team,
+      <c r="F5" t="str">
+        <v>Showcasing King Upholstery’s craftsmanship online</v>
+      </c>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi King Upholstery team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site retains a 2015–2021 footer, duplicated navigation and an inactive-looking embedded tweets area, while project imagery and quote steps lack a clear visual sequence. This matters because customers considering valuable furniture restoration may not see enough current craftsmanship proof before deciding whether to enquire.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a photo-led service structure, recent project gallery, simple estimate process, London coverage, testimonials and image-upload enquiry form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -717,15 +751,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Sent</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Showcasing King Upholstery’s craftsmanship online
-Hi King Upholstery team,
+      <c r="J5" t="str">
+        <v>Following up — Showcasing King Upholstery’s craftsmanship online</v>
+      </c>
+      <c r="K5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi King Upholstery team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a photo-led service structure, recent project gallery, simple estimate process, London coverage, testimonials and image-upload enquiry form. That would directly address the current issue where the site retains a 2015–2021 footer, duplicated navigation and an inactive-looking embedded tweets area, while project imagery and quote steps lack a clear visual sequence, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -735,15 +771,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Showcasing King Upholstery’s craftsmanship online
-Hi King Upholstery team,
+      <c r="L5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v>Final follow-up — Showcasing King Upholstery’s craftsmanship online</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi King Upholstery team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a photo-led service structure, recent project gallery, simple estimate process, London coverage, testimonials and image-upload enquiry form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -752,13 +790,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M5" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -778,9 +816,11 @@
       <c r="E6" t="str">
         <v/>
       </c>
-      <c r="F6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A modern showcase for Retouch Lighting
-Hi Retouch Lighting team,
+      <c r="F6" t="str">
+        <v>A modern showcase for Retouch Lighting</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Retouch Lighting team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the website still carries a 2014-era presentation and uses an email domain different from the website domain without explaining it; the restoration work is not organised into a strong visual portfolio. This matters because collectors and interior designers may hesitate if the contact identity feels inconsistent or the specialist workmanship is difficult to assess.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a premium restoration-led hero, service categories, before-and-after gallery, conservation process, trade-client pathway and clearer contact details. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -791,15 +831,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Sent</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A modern showcase for Retouch Lighting
-Hi Retouch Lighting team,
+      <c r="J6" t="str">
+        <v>Following up — A modern showcase for Retouch Lighting</v>
+      </c>
+      <c r="K6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Retouch Lighting team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a premium restoration-led hero, service categories, before-and-after gallery, conservation process, trade-client pathway and clearer contact details. That would directly address the current issue where the website still carries a 2014-era presentation and uses an email domain different from the website domain without explaining it; the restoration work is not organised into a strong visual portfolio, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -809,15 +851,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A modern showcase for Retouch Lighting
-Hi Retouch Lighting team,
+      <c r="L6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v>Final follow-up — A modern showcase for Retouch Lighting</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Retouch Lighting team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a premium restoration-led hero, service categories, before-and-after gallery, conservation process, trade-client pathway and clearer contact details, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -826,13 +870,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M6" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -852,9 +896,11 @@
       <c r="E7" t="str">
         <v>Facebook: https://www.facebook.com/PearcePearceSurveyorsLimited/</v>
       </c>
-      <c r="F7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Website clarity idea for Pearce &amp; Pearce Surveyors
-Hi Pearce &amp; Pearce Surveyors team,
+      <c r="F7" t="str">
+        <v>Website clarity idea for Pearce &amp; Pearce Surveyors</v>
+      </c>
+      <c r="G7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Pearce &amp; Pearce Surveyors team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site retains a 2013 footer and a narrow, dated content structure that gives limited prominence to party-wall surveying, snagging, turnaround expectations and case evidence. This matters because property owners comparing surveyors may not immediately understand the firm’s focus or what happens after an enquiry.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around clear service pathways, stronger credentials and case-study proof, an explained three-step process, FAQs and a concise consultation form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -865,15 +911,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Sent</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Website clarity idea for Pearce &amp; Pearce Surveyors
-Hi Pearce &amp; Pearce Surveyors team,
+      <c r="J7" t="str">
+        <v>Following up — Website clarity idea for Pearce &amp; Pearce Surveyors</v>
+      </c>
+      <c r="K7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Pearce &amp; Pearce Surveyors team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is clear service pathways, stronger credentials and case-study proof, an explained three-step process, FAQs and a concise consultation form. That would directly address the current issue where the site retains a 2013 footer and a narrow, dated content structure that gives limited prominence to party-wall surveying, snagging, turnaround expectations and case evidence, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -883,15 +931,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Website clarity idea for Pearce &amp; Pearce Surveyors
-Hi Pearce &amp; Pearce Surveyors team,
+      <c r="L7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v>Final follow-up — Website clarity idea for Pearce &amp; Pearce Surveyors</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Pearce &amp; Pearce Surveyors team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve clear service pathways, stronger credentials and case-study proof, an explained three-step process, FAQs and a concise consultation form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -900,13 +950,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M7" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -927,9 +977,11 @@
         <v xml:space="preserve">Facebook: https://www.instagram.com/able_waste/
 Facebook: https://www.facebook.com/ablewasteservices/</v>
       </c>
-      <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A faster quote journey for Able Waste Services
-Hi Able Waste Services team,
+      <c r="F8" t="str">
+        <v>A faster quote journey for Able Waste Services</v>
+      </c>
+      <c r="G8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Able Waste Services team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site has a dated 2013 visual framework and spreads important skip sizes, waste options, recycling proof and quote information across a long conventional navigation journey. This matters because households and trade customers may call competitors that make availability, coverage and quote requirements easier to understand.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a fast quote-led hero, clear service cards, skip guidance, recycling and licence proof, recent work, coverage and a postcode-aware enquiry form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -940,15 +992,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Sent</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A faster quote journey for Able Waste Services
-Hi Able Waste Services team,
+      <c r="J8" t="str">
+        <v>Following up — A faster quote journey for Able Waste Services</v>
+      </c>
+      <c r="K8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Able Waste Services team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a fast quote-led hero, clear service cards, skip guidance, recycling and licence proof, recent work, coverage and a postcode-aware enquiry form. That would directly address the current issue where the site has a dated 2013 visual framework and spreads important skip sizes, waste options, recycling proof and quote information across a long conventional navigation journey, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -958,15 +1012,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A faster quote journey for Able Waste Services
-Hi Able Waste Services team,
+      <c r="L8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v>Final follow-up — A faster quote journey for Able Waste Services</v>
+      </c>
+      <c r="O8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Able Waste Services team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a fast quote-led hero, clear service cards, skip guidance, recycling and licence proof, recent work, coverage and a postcode-aware enquiry form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -975,13 +1031,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M8" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -1001,9 +1057,11 @@
       <c r="E9" t="str">
         <v>Profile: https://www.computerrepaircompanies.co.uk/2890/go-4it-co-uk</v>
       </c>
-      <c r="F9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer support journey for GO-4IT.co.uk
-Hi GO-4IT.co.uk team,
+      <c r="F9" t="str">
+        <v>A clearer support journey for GO-4IT.co.uk</v>
+      </c>
+      <c r="G9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi GO-4IT.co.uk team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage is heavily optimised around repeated location phrases and device keywords, with a 2014–2025 footer and limited visual distinction between repair, data recovery, home support and business IT. This matters because visitors with an urgent problem may need to scan too much text before finding the right support option.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a concise problem-led hero, service comparison, response process, recent repair examples, West London coverage and a short booking form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1014,15 +1072,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Sent</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A clearer support journey for GO-4IT.co.uk
-Hi GO-4IT.co.uk team,
+      <c r="J9" t="str">
+        <v>Following up — A clearer support journey for GO-4IT.co.uk</v>
+      </c>
+      <c r="K9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi GO-4IT.co.uk team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a concise problem-led hero, service comparison, response process, recent repair examples, West London coverage and a short booking form. That would directly address the current issue where the homepage is heavily optimised around repeated location phrases and device keywords, with a 2014–2025 footer and limited visual distinction between repair, data recovery, home support and business IT, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1032,15 +1092,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A clearer support journey for GO-4IT.co.uk
-Hi GO-4IT.co.uk team,
+      <c r="L9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v>Final follow-up — A clearer support journey for GO-4IT.co.uk</v>
+      </c>
+      <c r="O9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi GO-4IT.co.uk team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a concise problem-led hero, service comparison, response process, recent repair examples, West London coverage and a short booking form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1049,13 +1111,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M9" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -1076,9 +1138,11 @@
         <v xml:space="preserve">Rightmove: https://www.rightmove.co.uk/estate-agents/agent/Orange-Square/London-9358.html
 Rightmove: https://www.getagent.co.uk/estate-agent/orange-square/798</v>
       </c>
-      <c r="F10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A stronger valuation journey for Orange Square
-Hi Orange Square team,
+      <c r="F10" t="str">
+        <v>A stronger valuation journey for Orange Square</v>
+      </c>
+      <c r="G10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Orange Square team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage uses an older 2014 presentation and does not give sales, lettings, management, valuations and current property listings a strong modern hierarchy. This matters because owners and landlords may find it harder to see local expertise, live inventory and the most relevant valuation action at a glance.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a property-led hero, separate seller and landlord journeys, current listing cards, local proof, valuation process, area guides and focused enquiry form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1089,15 +1153,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Sent</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A stronger valuation journey for Orange Square
-Hi Orange Square team,
+      <c r="J10" t="str">
+        <v>Following up — A stronger valuation journey for Orange Square</v>
+      </c>
+      <c r="K10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Orange Square team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a property-led hero, separate seller and landlord journeys, current listing cards, local proof, valuation process, area guides and focused enquiry form. That would directly address the current issue where the homepage uses an older 2014 presentation and does not give sales, lettings, management, valuations and current property listings a strong modern hierarchy, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1107,15 +1173,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A stronger valuation journey for Orange Square
-Hi Orange Square team,
+      <c r="L10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v>Final follow-up — A stronger valuation journey for Orange Square</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Orange Square team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a property-led hero, separate seller and landlord journeys, current listing cards, local proof, valuation process, area guides and focused enquiry form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1124,13 +1192,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M10" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -1150,9 +1218,11 @@
       <c r="E11" t="str">
         <v/>
       </c>
-      <c r="F11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer website journey for BelectriX
-Hi BelectriX Ltd team,
+      <c r="F11" t="str">
+        <v>A clearer website journey for BelectriX</v>
+      </c>
+      <c r="G11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi BelectriX Ltd team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the current site mixes dated styling with long technical service copy and inconsistent contact-number presentation, while project evidence and the quote path are not prominent enough. This matters because homeowners and commercial clients may not quickly understand coverage, credentials or which electrical service fits their need.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a clear service grid, compliance and qualification proof, recent projects, London and Hertfordshire coverage, FAQs and a streamlined quote form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1163,15 +1233,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Sent</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A clearer website journey for BelectriX
-Hi BelectriX Ltd team,
+      <c r="J11" t="str">
+        <v>Following up — A clearer website journey for BelectriX</v>
+      </c>
+      <c r="K11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi BelectriX Ltd team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a clear service grid, compliance and qualification proof, recent projects, London and Hertfordshire coverage, FAQs and a streamlined quote form. That would directly address the current issue where the current site mixes dated styling with long technical service copy and inconsistent contact-number presentation, while project evidence and the quote path are not prominent enough, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1181,15 +1253,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A clearer website journey for BelectriX
-Hi BelectriX Ltd team,
+      <c r="L11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v>Final follow-up — A clearer website journey for BelectriX</v>
+      </c>
+      <c r="O11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi BelectriX Ltd team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a clear service grid, compliance and qualification proof, recent projects, London and Hertfordshire coverage, FAQs and a streamlined quote form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1198,13 +1272,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M11" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -1225,9 +1299,11 @@
         <v xml:space="preserve">Facebook: https://www.instagram.com/fan.services/
 Facebook: https://www.facebook.com/fanservicesA2Z/</v>
       </c>
-      <c r="F12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Simplifying Fan Services’ enquiry journey
-Hi Fan Services Ltd team,
+      <c r="F12" t="str">
+        <v>Simplifying Fan Services’ enquiry journey</v>
+      </c>
+      <c r="G12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Fan Services Ltd team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage repeats introductory claims and is extremely dense with headings, borough lists and similar calls to action, making the technical offer difficult to scan. This matters because restaurant and facilities managers dealing with downtime may miss the quickest route to repairs, surveys or compliance information.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around an emergency-first hero, distinct installation/repair/cleaning pathways, compliance proof, project examples, maintenance plans and a site-survey form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1238,15 +1314,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Sent</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Simplifying Fan Services’ enquiry journey
-Hi Fan Services Ltd team,
+      <c r="J12" t="str">
+        <v>Following up — Simplifying Fan Services’ enquiry journey</v>
+      </c>
+      <c r="K12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Fan Services Ltd team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is an emergency-first hero, distinct installation/repair/cleaning pathways, compliance proof, project examples, maintenance plans and a site-survey form. That would directly address the current issue where the homepage repeats introductory claims and is extremely dense with headings, borough lists and similar calls to action, making the technical offer difficult to scan, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1256,15 +1334,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Simplifying Fan Services’ enquiry journey
-Hi Fan Services Ltd team,
+      <c r="L12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v>Final follow-up — Simplifying Fan Services’ enquiry journey</v>
+      </c>
+      <c r="O12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Fan Services Ltd team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve an emergency-first hero, distinct installation/repair/cleaning pathways, compliance proof, project examples, maintenance plans and a site-survey form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1273,13 +1353,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M12" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -1299,9 +1379,11 @@
       <c r="E13" t="str">
         <v>Facebook: https://www.facebook.com/heatmeplumbers/</v>
       </c>
-      <c r="F13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A more current homepage for HeatMe Plumbers
-Hi HeatMe Plumbers team,
+      <c r="F13" t="str">
+        <v>A more current homepage for HeatMe Plumbers</v>
+      </c>
+      <c r="G13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi HeatMe Plumbers team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the current site uses awkward wording, inconsistent spacing and a 2016–2020 footer, while urgent repairs, boiler work, bathrooms and service areas compete for attention. This matters because customers with heating or plumbing problems may question how current the business information is or fail to find the right enquiry route quickly.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around an urgent-call hero, clearer service categories, qualification proof, recent work, coverage, transparent process and a mobile-friendly quote form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1312,15 +1394,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Sent</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A more current homepage for HeatMe Plumbers
-Hi HeatMe Plumbers team,
+      <c r="J13" t="str">
+        <v>Following up — A more current homepage for HeatMe Plumbers</v>
+      </c>
+      <c r="K13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi HeatMe Plumbers team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is an urgent-call hero, clearer service categories, qualification proof, recent work, coverage, transparent process and a mobile-friendly quote form. That would directly address the current issue where the current site uses awkward wording, inconsistent spacing and a 2016–2020 footer, while urgent repairs, boiler work, bathrooms and service areas compete for attention, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1330,15 +1414,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A more current homepage for HeatMe Plumbers
-Hi HeatMe Plumbers team,
+      <c r="L13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v>Final follow-up — A more current homepage for HeatMe Plumbers</v>
+      </c>
+      <c r="O13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi HeatMe Plumbers team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve an urgent-call hero, clearer service categories, qualification proof, recent work, coverage, transparent process and a mobile-friendly quote form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1347,13 +1433,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M13" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -1373,9 +1459,11 @@
       <c r="E14" t="str">
         <v>Facebook: https://www.facebook.com/p/Crown-Cleaners-100063942528715/</v>
       </c>
-      <c r="F14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A stronger first impression for Crown Cleaners
-Hi Crown Cleaners team,
+      <c r="F14" t="str">
+        <v>A stronger first impression for Crown Cleaners</v>
+      </c>
+      <c r="G14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Crown Cleaners team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the website keeps a 2014–2025 footer and a generic, template-like layout with limited differentiation, recent-work proof or a short quote journey. This matters because Fulham customers comparing cleaners may not quickly see why the company is the best fit or feel confident that the site is actively maintained.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a service-specific hero, clearer packages, local credibility, photo-led work proof, coverage, FAQs and a concise cleaning quote form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1386,15 +1474,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Sent</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A stronger first impression for Crown Cleaners
-Hi Crown Cleaners team,
+      <c r="J14" t="str">
+        <v>Following up — A stronger first impression for Crown Cleaners</v>
+      </c>
+      <c r="K14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Crown Cleaners team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a service-specific hero, clearer packages, local credibility, photo-led work proof, coverage, FAQs and a concise cleaning quote form. That would directly address the current issue where the website keeps a 2014–2025 footer and a generic, template-like layout with limited differentiation, recent-work proof or a short quote journey, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1404,15 +1494,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A stronger first impression for Crown Cleaners
-Hi Crown Cleaners team,
+      <c r="L14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v>Final follow-up — A stronger first impression for Crown Cleaners</v>
+      </c>
+      <c r="O14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Crown Cleaners team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a service-specific hero, clearer packages, local credibility, photo-led work proof, coverage, FAQs and a concise cleaning quote form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1421,13 +1513,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M14" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -1448,9 +1540,11 @@
         <v xml:space="preserve">Facebook: https://www.facebook.com/londongutterclean/
 Facebook: https://www.trustpilot.com/review/www.londongutterclean.co.uk</v>
       </c>
-      <c r="F15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer quote journey for London Gutter Clean
-Hi London Gutter Clean team,
+      <c r="F15" t="str">
+        <v>A clearer quote journey for London Gutter Clean</v>
+      </c>
+      <c r="G15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Gutter Clean team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site is built around older long-form location pages and does not foreground before-and-after proof, repair options, guarantees and the fastest quote route consistently. This matters because homeowners may not immediately understand the difference between cleaning, repair and replacement or how to request the right service.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a clear quote-led homepage, service comparison, before-and-after projects, Which? and review proof, coverage map, FAQs and photo-upload enquiry. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1461,15 +1555,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Sent</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A clearer quote journey for London Gutter Clean
-Hi London Gutter Clean team,
+      <c r="J15" t="str">
+        <v>Following up — A clearer quote journey for London Gutter Clean</v>
+      </c>
+      <c r="K15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Gutter Clean team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a clear quote-led homepage, service comparison, before-and-after projects, Which? and review proof, coverage map, FAQs and photo-upload enquiry. That would directly address the current issue where the site is built around older long-form location pages and does not foreground before-and-after proof, repair options, guarantees and the fastest quote route consistently, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1479,15 +1575,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A clearer quote journey for London Gutter Clean
-Hi London Gutter Clean team,
+      <c r="L15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>Final follow-up — A clearer quote journey for London Gutter Clean</v>
+      </c>
+      <c r="O15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Gutter Clean team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a clear quote-led homepage, service comparison, before-and-after projects, Which? and review proof, coverage map, FAQs and photo-upload enquiry, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1496,13 +1594,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M15" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -1522,9 +1620,11 @@
       <c r="E16" t="str">
         <v/>
       </c>
-      <c r="F16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Replacing the broken Flash experience on Vinyl Touch
-Hi Vinyl Touch team,
+      <c r="F16" t="str">
+        <v>Replacing the broken Flash experience on Vinyl Touch</v>
+      </c>
+      <c r="G16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Vinyl Touch team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage explicitly says Flash is required, a technology modern browsers no longer support, so the main visual experience is effectively broken. This matters because prospective commercial clients cannot reliably view the company’s work, which is especially damaging for a highly visual vinyl and manifestation service.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a responsive project-led homepage, service categories, case studies, material benefits, installation process and a brief-led enquiry form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1535,15 +1635,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Sent</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Replacing the broken Flash experience on Vinyl Touch
-Hi Vinyl Touch team,
+      <c r="J16" t="str">
+        <v>Following up — Replacing the broken Flash experience on Vinyl Touch</v>
+      </c>
+      <c r="K16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Vinyl Touch team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a responsive project-led homepage, service categories, case studies, material benefits, installation process and a brief-led enquiry form. That would directly address the current issue where the homepage explicitly says Flash is required, a technology modern browsers no longer support, so the main visual experience is effectively broken, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1553,15 +1655,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Replacing the broken Flash experience on Vinyl Touch
-Hi Vinyl Touch team,
+      <c r="L16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>Final follow-up — Replacing the broken Flash experience on Vinyl Touch</v>
+      </c>
+      <c r="O16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Vinyl Touch team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a responsive project-led homepage, service categories, case studies, material benefits, installation process and a brief-led enquiry form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1570,13 +1674,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M16" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -1597,9 +1701,11 @@
         <v xml:space="preserve">Facebook
 LinkedIn</v>
       </c>
-      <c r="F17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A clearer digital journey for Shene Insurance
-Hi Shene Insurance team,
+      <c r="F17" t="str">
+        <v>A clearer digital journey for Shene Insurance</v>
+      </c>
+      <c r="G17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shene Insurance team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site retains an older framework, compact content blocks and dated callback journey that do not clearly separate personal and business insurance needs. This matters because new clients may need more effort to understand the broker’s local value, cover categories and next step.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around separate personal/business pathways, clearer local trust and team story, service cards, explained advice process, FAQs and a modern callback form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1610,15 +1716,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Sent</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A clearer digital journey for Shene Insurance
-Hi Shene Insurance team,
+      <c r="J17" t="str">
+        <v>Following up — A clearer digital journey for Shene Insurance</v>
+      </c>
+      <c r="K17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shene Insurance team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is separate personal/business pathways, clearer local trust and team story, service cards, explained advice process, FAQs and a modern callback form. That would directly address the current issue where the site retains an older framework, compact content blocks and dated callback journey that do not clearly separate personal and business insurance needs, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1628,15 +1736,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A clearer digital journey for Shene Insurance
-Hi Shene Insurance team,
+      <c r="L17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>Final follow-up — A clearer digital journey for Shene Insurance</v>
+      </c>
+      <c r="O17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shene Insurance team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve separate personal/business pathways, clearer local trust and team story, service cards, explained advice process, FAQs and a modern callback form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1645,13 +1755,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M17" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -1671,9 +1781,11 @@
       <c r="E18" t="str">
         <v>Facebook: https://www.facebook.com/61557157795292</v>
       </c>
-      <c r="F18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Modernising London Financial Solutions’ website
-Hi London Financial Solutions team,
+      <c r="F18" t="str">
+        <v>Modernising London Financial Solutions’ website</v>
+      </c>
+      <c r="G18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Financial Solutions team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site uses a 2013-era layout with duplicated footer contact blocks, inconsistent address presentation and dense service pages that do not guide different client types clearly. This matters because business owners may struggle to distinguish accounting, payroll, tax and strategy services or judge the firm’s current expertise.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a focused advisory hero, service and client-type pathways, team credibility, case outcomes, a simple three-step consultation journey and current contact details. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1684,15 +1796,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Sent</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Modernising London Financial Solutions’ website
-Hi London Financial Solutions team,
+      <c r="J18" t="str">
+        <v>Following up — Modernising London Financial Solutions’ website</v>
+      </c>
+      <c r="K18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Financial Solutions team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a focused advisory hero, service and client-type pathways, team credibility, case outcomes, a simple three-step consultation journey and current contact details. That would directly address the current issue where the site uses a 2013-era layout with duplicated footer contact blocks, inconsistent address presentation and dense service pages that do not guide different client types clearly, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1702,15 +1816,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Modernising London Financial Solutions’ website
-Hi London Financial Solutions team,
+      <c r="L18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v>Final follow-up — Modernising London Financial Solutions’ website</v>
+      </c>
+      <c r="O18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi London Financial Solutions team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a focused advisory hero, service and client-type pathways, team credibility, case outcomes, a simple three-step consultation journey and current contact details, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1719,13 +1835,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M18" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -1745,9 +1861,11 @@
       <c r="E19" t="str">
         <v>Facebook</v>
       </c>
-      <c r="F19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A more credible first impression for Accounts For You
-Hi Accounts For You team,
+      <c r="F19" t="str">
+        <v>A more credible first impression for Accounts For You</v>
+      </c>
+      <c r="G19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accounts For You team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the website still shows a 2012–2020 footer, includes Google+ in its social area and uses awkward copy and template-style service pages. This matters because outdated platform signals can reduce confidence for clients entrusting the firm with tax, payroll and company information.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a current professional homepage, service and business-stage pathways, clear team and compliance proof, client outcomes, FAQs and a free-consultation form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1758,15 +1876,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Sent</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A more credible first impression for Accounts For You
-Hi Accounts For You team,
+      <c r="J19" t="str">
+        <v>Following up — A more credible first impression for Accounts For You</v>
+      </c>
+      <c r="K19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accounts For You team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a current professional homepage, service and business-stage pathways, clear team and compliance proof, client outcomes, FAQs and a free-consultation form. That would directly address the current issue where the website still shows a 2012–2020 footer, includes Google+ in its social area and uses awkward copy and template-style service pages, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1776,15 +1896,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A more credible first impression for Accounts For You
-Hi Accounts For You team,
+      <c r="L19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v>Final follow-up — A more credible first impression for Accounts For You</v>
+      </c>
+      <c r="O19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Accounts For You team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a current professional homepage, service and business-stage pathways, clear team and compliance proof, client outcomes, FAQs and a free-consultation form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1793,13 +1915,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M19" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -1819,9 +1941,11 @@
       <c r="E20" t="str">
         <v/>
       </c>
-      <c r="F20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: A faster emergency journey for Master Refrigeration
-Hi Master Refrigeration team,
+      <c r="F20" t="str">
+        <v>A faster emergency journey for Master Refrigeration</v>
+      </c>
+      <c r="G20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Master Refrigeration team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the homepage repeats its main commercial-refrigeration paragraph, carries a 2014–2018 footer on service pages and uses awkward wording that weakens an urgent technical offer. This matters because restaurants and retailers facing equipment downtime may question how current the service is or miss the fastest engineer request route.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around an emergency-first hero, equipment-based service paths, response process, recent commercial work, maintenance plans, coverage and an engineer request form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1832,15 +1956,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Sent</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — A faster emergency journey for Master Refrigeration
-Hi Master Refrigeration team,
+      <c r="J20" t="str">
+        <v>Following up — A faster emergency journey for Master Refrigeration</v>
+      </c>
+      <c r="K20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Master Refrigeration team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is an emergency-first hero, equipment-based service paths, response process, recent commercial work, maintenance plans, coverage and an engineer request form. That would directly address the current issue where the homepage repeats its main commercial-refrigeration paragraph, carries a 2014–2018 footer on service pages and uses awkward wording that weakens an urgent technical offer, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1850,15 +1976,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — A faster emergency journey for Master Refrigeration
-Hi Master Refrigeration team,
+      <c r="L20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>Final follow-up — A faster emergency journey for Master Refrigeration</v>
+      </c>
+      <c r="O20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Master Refrigeration team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve an emergency-first hero, equipment-based service paths, response process, recent commercial work, maintenance plans, coverage and an engineer request form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1867,13 +1995,13 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M20" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -1893,9 +2021,11 @@
       <c r="E21" t="str">
         <v>Facebook: https://www.facebook.com/p/CF-Roofing-Ltd-100063945463235/</v>
       </c>
-      <c r="F21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Showcasing C.F. Roofing’s work more clearly
-Hi C.F. Roofing Ltd team,
+      <c r="F21" t="str">
+        <v>Showcasing C.F. Roofing’s work more clearly</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi C.F. Roofing Ltd team,
 I came across your business while researching established London companies whose website could better reflect the quality of their work. Your current service offering is clear enough to show genuine experience, which is why I thought a focused redesign could be worthwhile.
 While reviewing the website, I noticed that the site keeps a 2015 footer and relies on a broad sitemap-style structure, while its strongest assets—five-star feedback, workmanship and project photos—are not organised into a persuasive quote journey. This matters because homeowners may find it harder to compare roofing options, assess recent work and request the right inspection.
 I created a complimentary full-homepage redesign concept for your business. It reorganises the page around a service-led hero, pitched/flat/repair pathways, recent projects, review proof, coverage, clear process and a short photo-friendly quote form. The aim is not simply to make the site look newer, but to help visitors understand your value faster, build confidence and take the right next step on mobile or desktop.
@@ -1906,15 +2036,17 @@
 Web Developer
 Portfolio: ksnirob.com</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Sent</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>2026-09-09</v>
       </c>
-      <c r="I21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Following up — Showcasing C.F. Roofing’s work more clearly
-Hi C.F. Roofing Ltd team,
+      <c r="J21" t="str">
+        <v>Following up — Showcasing C.F. Roofing’s work more clearly</v>
+      </c>
+      <c r="K21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi C.F. Roofing Ltd team,
 I wanted to follow up on the homepage redesign concept I sent. The first change I would prioritise is a service-led hero, pitched/flat/repair pathways, recent projects, review proof, coverage, clear process and a short photo-friendly quote form. That would directly address the current issue where the site keeps a 2015 footer and relies on a broad sitemap-style structure, while its strongest assets—five-star feedback, workmanship and project photos—are not organised into a persuasive quote journey, and make it easier for prospective customers to take action.
 To keep the next step straightforward and low-risk, a focused redesign like this would usually cost US$200–$800 as a one-time fee, depending on the final pages and features you require. We would agree the exact scope and price before work begins. No upfront payment is required; you would pay only after the agreed website has been delivered and you are happy with it. Domain, hosting and any paid third-party services would be discussed separately if needed.
 Would it be helpful if I sent a short page-by-page plan with the recommended priorities?
@@ -1924,15 +2056,17 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="J21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Subject: Final follow-up — Showcasing C.F. Roofing’s work more clearly
-Hi C.F. Roofing Ltd team,
+      <c r="L21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v>Final follow-up — Showcasing C.F. Roofing’s work more clearly</v>
+      </c>
+      <c r="O21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi C.F. Roofing Ltd team,
 One final follow-up regarding the homepage concept. The main opportunity is still to improve a service-led hero, pitched/flat/repair pathways, recent projects, review proof, coverage, clear process and a short photo-friendly quote form, so visitors can understand the business quickly and enquire with less friction.
 I understand that a website update may not be a priority right now. If the idea is relevant, I can send a concise scope and timeline for you to review with no obligation. If the timing is not right, simply reply “later” or “not interested” and I will close the loop.
 Kind regards,
@@ -1941,26 +2075,26 @@
 Portfolio: ksnirob.com
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
-      <c r="M21" t="str">
-        <v>Draft</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
+        <v>Draft</v>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
   </ignoredErrors>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="G2:G1000 J2:J1000 M2:M1000">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
       <formula1>"Draft,Sent,Replied,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O2:O1000">
-      <formula1>"Win,Closed"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
+      <formula1>"Win,Lost"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/excel/Batch_04_Leads_Tracker.xlsx
+++ b/excel/Batch_04_Leads_Tracker.xlsx
@@ -418,8 +418,6 @@
     <col min="16" max="16" width="18.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="32.83203125" customWidth="1"/>
-    <col min="20" max="20" width="42.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1717,10 +1715,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H17" t="str">
-        <v>Sent</v>
+        <v>Draft</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-09-09</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v>Following up — A clearer digital journey for Shene Insurance</v>

--- a/excel/Batch_04_Leads_Tracker.xlsx
+++ b/excel/Batch_04_Leads_Tracker.xlsx
@@ -2089,7 +2089,7 @@
   </ignoredErrors>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="H2:H1000 L2:L1000 P2:P1000">
-      <formula1>"Draft,Sent,Replied,Closed"</formula1>
+      <formula1>"Draft,Sent,Replied,Mail Not Found,Bounce Back,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1000">
       <formula1>"Win,Lost"</formula1>

--- a/excel/Batch_04_Leads_Tracker.xlsx
+++ b/excel/Batch_04_Leads_Tracker.xlsx
@@ -528,10 +528,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N2" t="str">
         <v>Final follow-up — Homepage redesign idea for Spring Clean London</v>
@@ -609,10 +609,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N3" t="str">
         <v>Final follow-up — A clearer online experience for P Shah Opticians</v>
@@ -689,10 +689,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N4" t="str">
         <v>Final follow-up — A more refined homepage for Bespoke Tailor Studio</v>
@@ -770,10 +770,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N5" t="str">
         <v>Final follow-up — Showcasing King Upholstery’s craftsmanship online</v>
@@ -850,10 +850,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N6" t="str">
         <v>Final follow-up — A modern showcase for Retouch Lighting</v>
@@ -930,10 +930,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N7" t="str">
         <v>Final follow-up — Website clarity idea for Pearce &amp; Pearce Surveyors</v>
@@ -1011,10 +1011,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N8" t="str">
         <v>Final follow-up — A faster quote journey for Able Waste Services</v>
@@ -1091,10 +1091,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N9" t="str">
         <v>Final follow-up — A clearer support journey for GO-4IT.co.uk</v>
@@ -1172,10 +1172,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N10" t="str">
         <v>Final follow-up — A stronger valuation journey for Orange Square</v>
@@ -1252,10 +1252,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N11" t="str">
         <v>Final follow-up — A clearer website journey for BelectriX</v>
@@ -1333,10 +1333,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N12" t="str">
         <v>Final follow-up — Simplifying Fan Services’ enquiry journey</v>
@@ -1413,10 +1413,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N13" t="str">
         <v>Final follow-up — A more current homepage for HeatMe Plumbers</v>
@@ -1493,10 +1493,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N14" t="str">
         <v>Final follow-up — A stronger first impression for Crown Cleaners</v>
@@ -1574,10 +1574,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N15" t="str">
         <v>Final follow-up — A clearer quote journey for London Gutter Clean</v>
@@ -1654,10 +1654,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N16" t="str">
         <v>Final follow-up — Replacing the broken Flash experience on Vinyl Touch</v>
@@ -1696,8 +1696,8 @@
         <v>020 8878 7822</v>
       </c>
       <c r="E17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-LinkedIn</v>
+        <v xml:space="preserve">Facebook: Facebook
+LinkedIn: LinkedIn</v>
       </c>
       <c r="F17" t="str">
         <v>A clearer digital journey for Shene Insurance</v>
@@ -1715,10 +1715,10 @@
 Portfolio: ksnirob.com</v>
       </c>
       <c r="H17" t="str">
-        <v>Draft</v>
+        <v>Bounce Back</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="J17" t="str">
         <v>Following up — A clearer digital journey for Shene Insurance</v>
@@ -1815,10 +1815,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N18" t="str">
         <v>Final follow-up — Modernising London Financial Solutions’ website</v>
@@ -1857,7 +1857,7 @@
         <v>07931 388060 / 020 8983 8255</v>
       </c>
       <c r="E19" t="str">
-        <v>Facebook</v>
+        <v>Facebook: Facebook</v>
       </c>
       <c r="F19" t="str">
         <v>A more credible first impression for Accounts For You</v>
@@ -1895,10 +1895,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N19" t="str">
         <v>Final follow-up — A more credible first impression for Accounts For You</v>
@@ -1975,10 +1975,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N20" t="str">
         <v>Final follow-up — A faster emergency journey for Master Refrigeration</v>
@@ -2055,10 +2055,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-18</v>
       </c>
       <c r="N21" t="str">
         <v>Final follow-up — Showcasing C.F. Roofing’s work more clearly</v>
